--- a/AAII_Financials/Quarterly/SSDOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSDOY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="92">
   <si>
     <t>SSDOY</t>
   </si>
@@ -656,167 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
-      </c>
-      <c r="K7" s="2">
-        <v>45199</v>
       </c>
       <c r="L7" s="2">
         <v>45199</v>
       </c>
       <c r="M7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -853,86 +857,89 @@
       <c r="N8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="3">
         <v>2162700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1718400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1748200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1553900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1934200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1680400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1899100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1680200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1958700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1837400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1487300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1998900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2595600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2591400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2665800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2629500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2728800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2537700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2443700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2384400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2475700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2342200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2166500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2061900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2018600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1866700</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -969,86 +976,89 @@
       <c r="N9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="3">
         <v>601700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>599900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>534600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>446500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>525100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>454700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>504900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>451000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>528300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>510000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>397800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>438700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>697900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>575600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>540600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>543800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>583700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>566900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>492100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>496600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>568900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>542200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>487700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>483100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>504900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>461500</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1085,86 +1095,89 @@
       <c r="N10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10" s="3">
         <v>1561000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1118600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1213600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1107400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1409100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1225700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1394200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1229200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1430400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1327400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1089400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1560200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1897800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2015700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2125200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2085700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2145100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1970800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1951600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1887800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1906800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1800000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1678700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1578800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1513700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1405200</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1205,8 +1218,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1321,8 +1335,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1437,8 +1454,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1475,86 +1495,89 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>-600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-69800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-18300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-10300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>32700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-986200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>211700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>219700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>30900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>122500</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>15300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>10900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>4500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>49300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>29600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>4600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>32800</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>648600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>26400</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>5400</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>28900</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1591,8 +1614,8 @@
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1669,8 +1692,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1708,8 +1734,9 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1746,86 +1773,89 @@
       <c r="N17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="3">
         <v>2085300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1599200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1663300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1524900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1899900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>838500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2007000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1726300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1945200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1730400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1687100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1941700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2515200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2278300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2401500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2259800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2712600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2285800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2230500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1960000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2420100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2665500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2097600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1853200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2064800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1705100</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1862,86 +1892,89 @@
       <c r="N18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="3">
         <v>77500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>119200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>84900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>29100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>34200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>841900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-107900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-46100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>13500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>107000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-199800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>57200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>80400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>313000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>264400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>369700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>16200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>251900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>213200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>424400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>55600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-323300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>68900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>208700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-46200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>161600</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1982,8 +2015,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2020,86 +2054,89 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3">
         <v>-28900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>32700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>25100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-9000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>7500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>52400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-10600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-14500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-11300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>4900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>13500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>33600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>6000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>335200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>9700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>1400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>11000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2136,86 +2173,89 @@
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>181700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>236300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>247000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>178400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>175200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>964000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>43100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>84900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>194900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>222400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-87400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>208800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>220600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>446000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>394200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>502600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>140600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>354300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>342900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>525800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>490600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-215000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>165900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>306600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>62700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2264,74 +2304,77 @@
       <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T22" s="3">
         <v>1900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>3600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>6200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>6400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>6200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>6100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1900</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>1600</v>
       </c>
       <c r="AG22" s="3">
         <v>1600</v>
       </c>
       <c r="AH22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AI22" s="3">
         <v>1900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>2200</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>1900</v>
       </c>
       <c r="AL22" s="3">
         <v>1900</v>
       </c>
       <c r="AM22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AN22" s="3">
         <v>2000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2368,86 +2411,89 @@
       <c r="N23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="3">
         <v>48600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>114700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>117700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>54100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>33200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>828600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-108100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-42100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>62100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>92800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-218500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>49600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>62700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>310500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>256200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>372300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>27700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>250900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>245100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>428500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>387900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-315800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>64200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>208200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-37200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>168400</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2484,86 +2530,89 @@
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="3">
         <v>7100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>31300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>30100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>16400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>27900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>282400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>17400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>28900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>37900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>23900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-37200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>31900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>43400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>119400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>78600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>35900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>47900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>90300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>75600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>147300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>26200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-3700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>24400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>71000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>2900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>52400</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2678,8 +2727,11 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2716,86 +2768,89 @@
       <c r="N26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="3">
         <v>41400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>83400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>87600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>37700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>546200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-125500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-71000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>24200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>68900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-181200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>17600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>19200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>191200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>177600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>336300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-20200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>160600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>169500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>281200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>361700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-312100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>39800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>137200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-40100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>116000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2832,86 +2887,89 @@
       <c r="N27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P27" s="3">
         <v>36600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>81700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>79800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>29200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>537300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-125600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-85200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>14700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>60000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-177400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>12400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>10100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>183900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>173500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>322000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-24500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>151700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>170900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>261000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>359000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-323300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>43400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>124200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-45000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>112500</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3026,8 +3084,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3064,8 +3125,8 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -3142,8 +3203,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3258,8 +3322,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3374,8 +3441,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3412,86 +3482,89 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3">
         <v>28900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-32700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-25100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>9000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-7500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-52400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>10600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>14500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>11300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-4900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-13500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-33600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-335200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-9700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>2800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3528,86 +3601,89 @@
       <c r="N33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P33" s="3">
         <v>36600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>81700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>79800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>29200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>537300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-125600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-85200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>14700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>60000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-177400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>12400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>10100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>183900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>173500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>322000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-24500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>151700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>170900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>261000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>359000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-323300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>43400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>124200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-45000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>112500</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3722,8 +3798,11 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3760,207 +3839,213 @@
       <c r="N35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P35" s="3">
         <v>36600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>81700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>79800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>29200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>537300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-125600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-85200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>14700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>60000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-177400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>12400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>10100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>183900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>173500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>322000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-24500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>151700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>170900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>261000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>359000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-323300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>43400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>124200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-45000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>112500</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
-      </c>
-      <c r="K38" s="2">
-        <v>45199</v>
       </c>
       <c r="L38" s="2">
         <v>45199</v>
       </c>
       <c r="M38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4001,8 +4086,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4043,142 +4129,146 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>650100</v>
+      </c>
+      <c r="E41" s="3">
         <v>585800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>565000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>562300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>626400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>571000</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K41" s="3">
         <v>742600</v>
-      </c>
-      <c r="K41" s="3">
-        <v>754800</v>
       </c>
       <c r="L41" s="3">
         <v>754800</v>
       </c>
       <c r="M41" s="3">
+        <v>754800</v>
+      </c>
+      <c r="N41" s="3">
         <v>716900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>746700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>845200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>694800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>747200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>876300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3332400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1160100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>991500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>920400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>953000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>856500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>779000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>874900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1005200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>922200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>941300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1072000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1188400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1269900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1453200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1129400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1506900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1142100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1029500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>865700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1065500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1064500</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>178200</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>164400</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -4198,35 +4288,35 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>131300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>102600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>127900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>120200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>112900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>43300</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V42" s="3">
+      <c r="V42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W42" s="3">
         <v>14200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>153900</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>8</v>
       </c>
@@ -4242,853 +4332,877 @@
       <c r="AC42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF42" s="3">
+      <c r="AD42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG42" s="3">
         <v>17800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>43400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>88300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>70300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>160200</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>153800</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>131900</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>70100</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>95300</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>964100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1182300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>962900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>969900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1102700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>964300</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="3">
         <v>1061900</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1035000</v>
       </c>
       <c r="L43" s="3">
         <v>1035000</v>
       </c>
       <c r="M43" s="3">
+        <v>1035000</v>
+      </c>
+      <c r="N43" s="3">
         <v>1141800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1235200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1292700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1273400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1219000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1114200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3192200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1098300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1029500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1059000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1034100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1084400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1005400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1314800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1550200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1577000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1533500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1729700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1552900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1587200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1396500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1578100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1449400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1498200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1261200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1275100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1196000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1121300</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>932800</v>
+      </c>
+      <c r="E44" s="3">
         <v>938400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1041900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1024700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1020900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1039800</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" s="3">
         <v>1061600</v>
-      </c>
-      <c r="K44" s="3">
-        <v>1027100</v>
       </c>
       <c r="L44" s="3">
         <v>1027100</v>
       </c>
       <c r="M44" s="3">
+        <v>1027100</v>
+      </c>
+      <c r="N44" s="3">
         <v>982100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1013200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>929700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>945400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1022000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>926900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2830800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1074100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1216600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1185600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1246300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1454200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1517400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1684500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1649900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1587600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1546800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1579400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2828000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1378200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1287600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1179600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1174800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1237400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1182300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1087200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1026000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>981200</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>409800</v>
+      </c>
+      <c r="E45" s="3">
         <v>42000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>448000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>447400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>47100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>422700</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>373600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>418400</v>
       </c>
       <c r="L45" s="3">
         <v>418400</v>
       </c>
       <c r="M45" s="3">
+        <v>418400</v>
+      </c>
+      <c r="N45" s="3">
         <v>395600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>648000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>523200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>480900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>384000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>319800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>323200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>360600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>315000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>310200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>385800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>384400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>470100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>567500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>646900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>563200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>498100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>450700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>684400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>605200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>562200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>483100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>555800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>499200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>476200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>423900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>473300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>503300</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2956800</v>
+      </c>
+      <c r="E46" s="3">
         <v>3007300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3017900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3004300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3039100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2997700</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K46" s="3">
         <v>3334300</v>
-      </c>
-      <c r="K46" s="3">
-        <v>3235300</v>
       </c>
       <c r="L46" s="3">
         <v>3235300</v>
       </c>
       <c r="M46" s="3">
+        <v>3235300</v>
+      </c>
+      <c r="N46" s="3">
         <v>3236400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3643100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3722000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3497000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3500000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3357400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3523800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3736400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3552600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3489300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3773200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3779700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3772000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4441700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4852200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4650000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4519700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4831800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4559500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4858200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4742800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4458500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4757300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4537100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4102800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3783900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3831000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>3765600</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>909700</v>
+      </c>
+      <c r="E47" s="3">
         <v>187000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>750400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>19300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>166400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>727000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>866200</v>
-      </c>
-      <c r="K47" s="3">
-        <v>814200</v>
       </c>
       <c r="L47" s="3">
         <v>814200</v>
       </c>
       <c r="M47" s="3">
+        <v>814200</v>
+      </c>
+      <c r="N47" s="3">
         <v>823500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>809300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>711700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>665900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>711600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>653500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>936200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>87700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>91500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>100300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>98100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>103700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>105500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>124000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>126500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>153500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>171900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>229600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>216700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>223900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>221200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>239000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>236200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>241200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>237300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>221300</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>443500</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>200200</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2252500</v>
+      </c>
+      <c r="E48" s="3">
         <v>2371300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2636100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2580200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2539700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2480600</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K48" s="3">
         <v>2854600</v>
-      </c>
-      <c r="K48" s="3">
-        <v>2733700</v>
       </c>
       <c r="L48" s="3">
         <v>2733700</v>
       </c>
       <c r="M48" s="3">
+        <v>2733700</v>
+      </c>
+      <c r="N48" s="3">
         <v>2899200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3184000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3071600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2841100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3141600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3097500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8883900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2585200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2655700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2596400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2499900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2510000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2485100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2742100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2867400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2663100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2599100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2574700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2220100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1875500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1701900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1417000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1434500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1454700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1444700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1390800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1385400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1212100</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1454600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1498300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1890200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1861400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1828000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1785400</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>1417400</v>
-      </c>
-      <c r="K49" s="3">
-        <v>1366900</v>
       </c>
       <c r="L49" s="3">
         <v>1366900</v>
       </c>
       <c r="M49" s="3">
+        <v>1366900</v>
+      </c>
+      <c r="N49" s="3">
         <v>1365500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1391100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1285800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1182200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1183000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1057000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2794800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1289900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1358300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1661200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1769400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1908900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1941900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2185700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2270300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1450600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1474500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1581200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1561400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1577800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1497900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1487700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1524000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1551000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2185500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2131300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2185000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1313900</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5203,8 +5317,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5319,31 +5436,34 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
         <v>426400</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
       <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
         <v>709100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>275200</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -5358,85 +5478,88 @@
         <v>0</v>
       </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>493300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>478000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>511700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>483600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>773800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>823800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>711400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>746100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>686400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>827700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>824800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>888800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>986800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1010800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1029200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1143600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>973000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>643700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>625900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>593000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>630800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>666100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>677500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>652500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>665800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>617400</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5551,124 +5674,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7837000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8082600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8668100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8549800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8471200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8392300</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K54" s="3">
         <v>8906600</v>
-      </c>
-      <c r="K54" s="3">
-        <v>8594400</v>
       </c>
       <c r="L54" s="3">
         <v>8594400</v>
       </c>
       <c r="M54" s="3">
+        <v>8594400</v>
+      </c>
+      <c r="N54" s="3">
         <v>8780200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9521600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9284400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8664100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9047800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8648900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8937700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8523000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8369400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8593400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8827000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9130000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9129300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10382300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>11103200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9928000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9794500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>10360900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9530800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9179100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>8789600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>8195200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>8582800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>8450000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>8647800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>8179700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>8289800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>7109300</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5709,8 +5838,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5751,704 +5881,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>645000</v>
+      </c>
+      <c r="E57" s="3">
         <v>128200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>808900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>846500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>142100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>912000</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" s="3">
         <v>1266500</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1080200</v>
       </c>
       <c r="L57" s="3">
         <v>1080200</v>
       </c>
       <c r="M57" s="3">
+        <v>1080200</v>
+      </c>
+      <c r="N57" s="3">
         <v>1094900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1404300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1446800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1192400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1233100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1355500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1870900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>475800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>514500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>533700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>563900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>452800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>612400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>713100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>883100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>786600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>837400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>978100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>965600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>904700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>935900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>739700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>786800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>721900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>705300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>658500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>739700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>615300</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>576700</v>
+      </c>
+      <c r="E58" s="3">
         <v>320200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>784100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>920600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>815600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>772400</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>510200</v>
-      </c>
-      <c r="K58" s="3">
-        <v>563300</v>
       </c>
       <c r="L58" s="3">
         <v>563300</v>
       </c>
       <c r="M58" s="3">
+        <v>563300</v>
+      </c>
+      <c r="N58" s="3">
         <v>592100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>751300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>353200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>555300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>609200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>505600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>566200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>257500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>504900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>471500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>572300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1629900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1611100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1157000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1338600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>454700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>312000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>587400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>143500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>82100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>67400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>94400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>96400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>187700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>148300</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>169800</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>146900</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>459200</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>927400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1088600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>833700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>742900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>983200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>928200</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>438600</v>
-      </c>
-      <c r="K59" s="3">
-        <v>859100</v>
       </c>
       <c r="L59" s="3">
         <v>859100</v>
       </c>
       <c r="M59" s="3">
+        <v>859100</v>
+      </c>
+      <c r="N59" s="3">
         <v>844600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>818700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>965900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>860500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>904900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>816800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2203200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1847900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1487000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1341600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1451200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1322200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1199600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1477900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2007900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1800900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1805200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1952500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2099900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1686900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1564400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1333200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1750900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1483700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1360000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1143200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1301600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1073900</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2149100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2200400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2426700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2510000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2535100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2612600</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K60" s="3">
         <v>2613100</v>
-      </c>
-      <c r="K60" s="3">
-        <v>2502700</v>
       </c>
       <c r="L60" s="3">
         <v>2502700</v>
       </c>
       <c r="M60" s="3">
+        <v>2502700</v>
+      </c>
+      <c r="N60" s="3">
         <v>2531600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2974300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2765900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2608300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2747200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2677900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2841200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2581200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2506400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2346800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2587300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3404900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3423000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3348100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4229500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3042200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2954600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3518000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3209000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2673700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2567800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2167200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2634100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2393300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2213700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1971500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2188100</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2148300</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1495900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1740900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1558300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1528500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1494300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1186900</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>1483100</v>
-      </c>
-      <c r="K61" s="3">
-        <v>1407600</v>
       </c>
       <c r="L61" s="3">
         <v>1407600</v>
       </c>
       <c r="M61" s="3">
+        <v>1407600</v>
+      </c>
+      <c r="N61" s="3">
         <v>1468200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1605900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1756800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1559000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1658400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1746900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1819300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1484500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1845400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1896100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2189200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>919700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>913300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1425400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1380500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>939700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>943900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>725400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1083100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>658800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>641700</v>
-      </c>
-      <c r="AH61" s="3">
-        <v>640000</v>
       </c>
       <c r="AI61" s="3">
         <v>640000</v>
       </c>
       <c r="AJ61" s="3">
+        <v>640000</v>
+      </c>
+      <c r="AK61" s="3">
         <v>1028800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1024100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1013700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>922700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>571100</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>113500</v>
+      </c>
+      <c r="E62" s="3">
         <v>74600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>220100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>217600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>178400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>226900</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
         <v>140300</v>
-      </c>
-      <c r="K62" s="3">
-        <v>140100</v>
       </c>
       <c r="L62" s="3">
         <v>140100</v>
       </c>
       <c r="M62" s="3">
+        <v>140100</v>
+      </c>
+      <c r="N62" s="3">
         <v>143800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>155800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>318800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>396100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>418800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>402100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>693900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>489600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>333100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>673100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>337200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1055000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1055100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1168900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>775500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1254600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1266400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1337800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1332200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1283300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1272200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1257900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1278000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1460200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1549600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1499700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1508000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>963200</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6563,8 +6712,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6679,8 +6831,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6795,124 +6950,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3813800</v>
+      </c>
+      <c r="E66" s="3">
         <v>4120100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4272800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4316000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4307400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4154300</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K66" s="3">
         <v>4363600</v>
-      </c>
-      <c r="K66" s="3">
-        <v>4249600</v>
       </c>
       <c r="L66" s="3">
         <v>4249600</v>
       </c>
       <c r="M66" s="3">
+        <v>4249600</v>
+      </c>
+      <c r="N66" s="3">
         <v>4347700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4946900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4994100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4702800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4974600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4982600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5223200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4702800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4830300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5078700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5266900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5529100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5531500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6119600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6569200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5409600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5332000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5781800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5287200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4807400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4658000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4273400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4746900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5071500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4964400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>4674800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>4797000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>3839200</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6953,8 +7114,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7069,8 +7231,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7185,8 +7350,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7301,8 +7469,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7417,124 +7588,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2108300</v>
+      </c>
+      <c r="E72" s="3">
         <v>2044900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2516000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2380300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2269900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2290600</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K72" s="3">
         <v>2697200</v>
-      </c>
-      <c r="K72" s="3">
-        <v>2498100</v>
       </c>
       <c r="L72" s="3">
         <v>2498100</v>
       </c>
       <c r="M72" s="3">
+        <v>2498100</v>
+      </c>
+      <c r="N72" s="3">
         <v>2604200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2808000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2803600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2425100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2538900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2420500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5080900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2607000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2322100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2351600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2501100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2641600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2644200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3190500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3395300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>3405300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3320300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3302000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3020400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2997200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2856600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2672800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2463900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2104600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>2472500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>2383300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>2295800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>2341000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7649,8 +7826,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7765,8 +7945,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7881,124 +8064,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3916600</v>
+      </c>
+      <c r="E76" s="3">
         <v>3831600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4255300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4093000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4022900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4107600</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K76" s="3">
         <v>4389500</v>
-      </c>
-      <c r="K76" s="3">
-        <v>4208000</v>
       </c>
       <c r="L76" s="3">
         <v>4208000</v>
       </c>
       <c r="M76" s="3">
+        <v>4208000</v>
+      </c>
+      <c r="N76" s="3">
         <v>4295600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4423200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4290200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3961300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4073300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3666400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3714600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3820300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3539100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3514700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3560100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3600800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3597800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4262600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4534100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4518400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4462500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4579100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4243600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4371700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4131600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3921800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3835900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3378500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3683400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3504900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3492900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3270000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8113,129 +8302,135 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
-      </c>
-      <c r="K80" s="2">
-        <v>45199</v>
       </c>
       <c r="L80" s="2">
         <v>45199</v>
       </c>
       <c r="M80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8272,86 +8467,89 @@
       <c r="N81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P81" s="3">
         <v>36600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>81700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>79800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>29200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>537300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-125600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-85200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>14700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>60000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-177400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>12400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>10100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>183900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>173500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>322000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-24500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>151700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>170900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>261000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>359000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-323300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>43400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>124200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-45000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>112500</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8392,124 +8590,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E83" s="3">
         <v>115800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>124500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>143900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>126300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>127100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>135200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>142100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>131700</v>
       </c>
       <c r="L83" s="3">
         <v>131700</v>
       </c>
       <c r="M83" s="3">
+        <v>131700</v>
+      </c>
+      <c r="N83" s="3">
         <v>141300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>154100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>133100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>121600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>129400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>124300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>150900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>143500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>173800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>123400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>129000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>126000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>127000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>153000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>151500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>129300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>131800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>128100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>111000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>101900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>96100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>95400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>99800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>98500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>99800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>96500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>97900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>82900</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8624,8 +8826,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8740,8 +8945,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8856,8 +9064,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8972,8 +9183,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9088,73 +9302,76 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>199800</v>
+      </c>
+      <c r="E89" s="3">
         <v>308400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>245400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>16600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>34400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>174400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>23500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>198000</v>
-      </c>
-      <c r="K89" s="3">
-        <v>116700</v>
       </c>
       <c r="L89" s="3">
         <v>116700</v>
       </c>
       <c r="M89" s="3">
+        <v>116700</v>
+      </c>
+      <c r="N89" s="3">
         <v>281700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>22200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>458200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>98200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-229500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>381100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>34300</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
+      <c r="X89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y89" s="3">
         <v>0</v>
@@ -9204,8 +9421,11 @@
       <c r="AN89" s="3">
         <v>0</v>
       </c>
+      <c r="AO89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9246,73 +9466,74 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-52700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-25700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-45900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-49900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-29800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-46700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-65200</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-43100</v>
       </c>
       <c r="L91" s="3">
         <v>-43100</v>
       </c>
       <c r="M91" s="3">
+        <v>-43100</v>
+      </c>
+      <c r="N91" s="3">
         <v>-44000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-35400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-18819000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13874000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-21717000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11794000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13754000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-18010000</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -9362,8 +9583,11 @@
       <c r="AN91" s="3">
         <v>0</v>
       </c>
+      <c r="AO91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9478,8 +9702,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9594,73 +9821,76 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-85900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-38600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-99100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-76800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>27000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-419200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-129700</v>
-      </c>
-      <c r="K94" s="3">
-        <v>43600</v>
       </c>
       <c r="L94" s="3">
         <v>43600</v>
       </c>
       <c r="M94" s="3">
+        <v>43600</v>
+      </c>
+      <c r="N94" s="3">
         <v>-172100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>8400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-125500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>10900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-108900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-61000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>15400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>821000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -9710,8 +9940,11 @@
       <c r="AN94" s="3">
         <v>0</v>
       </c>
+      <c r="AO94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9752,65 +9985,66 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E96" s="3">
         <v>1400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>25700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>76400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>77600</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3">
         <v>-4200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-59900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-76700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-55700</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -9868,8 +10102,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9984,8 +10221,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10100,8 +10340,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10216,73 +10459,76 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-111300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-168400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-224900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>101400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-219300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>276100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-118100</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-118700</v>
       </c>
       <c r="L100" s="3">
         <v>-118700</v>
       </c>
       <c r="M100" s="3">
+        <v>-118700</v>
+      </c>
+      <c r="N100" s="3">
         <v>-175200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-119800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-233300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-133300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-92300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>99900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-294300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-703200</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="X100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
@@ -10332,73 +10578,76 @@
       <c r="AN100" s="3">
         <v>0</v>
       </c>
+      <c r="AO100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E101" s="3">
         <v>27100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>25000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-12800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>21500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>30100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>11500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-29400</v>
-      </c>
-      <c r="K101" s="3">
-        <v>12700</v>
       </c>
       <c r="L101" s="3">
         <v>12700</v>
       </c>
       <c r="M101" s="3">
+        <v>12700</v>
+      </c>
+      <c r="N101" s="3">
         <v>58000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>34400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-27500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>11800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>53100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>27700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>28000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-800</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -10448,73 +10697,76 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>85400</v>
+      </c>
+      <c r="E102" s="3">
         <v>87200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-18600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-95300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>85900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-94600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-62500</v>
-      </c>
-      <c r="K102" s="3">
-        <v>63100</v>
       </c>
       <c r="L102" s="3">
         <v>63100</v>
       </c>
       <c r="M102" s="3">
+        <v>63100</v>
+      </c>
+      <c r="N102" s="3">
         <v>-35500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-77900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>71900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-142300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-162900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>31500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>210800</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
+      <c r="X102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y102" s="3">
         <v>0</v>
@@ -10562,6 +10814,9 @@
         <v>0</v>
       </c>
       <c r="AN102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="3">
         <v>0</v>
       </c>
     </row>
